--- a/registration_forms/042_grip_application_form--registration_forms.xlsx
+++ b/registration_forms/042_grip_application_form--registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,7 +442,7 @@
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
     <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -914,7 +914,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>References</t>
+          <t>Upload References</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -968,7 +968,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Agree</t>
+          <t>Agree Privacy</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>first_name</t>
+          <t>first_name_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>First Name 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -1013,12 +1013,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>last_name</t>
+          <t>last_name_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>Last Name 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -1036,12 +1036,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>role</t>
+          <t>role_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Role</t>
+          <t>Role 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1059,12 +1059,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>contact_number</t>
+          <t>contact_number_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Contact Number</t>
+          <t>Contact Number 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1082,12 +1082,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>experience</t>
+          <t>experience_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Experience</t>
+          <t>Experience 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Equipment List</t>
+          <t>Upload Equipment</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1133,7 +1133,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Skills</t>
+          <t>Upload Skills</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1284,7 +1284,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>role_choices</t>
+          <t>role_2_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1301,7 +1301,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>role_choices</t>
+          <t>role_2_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
